--- a/data/trans_dic/P15D$urgencias-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 70,03</t>
+          <t>9,39; 62,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,6; 74,65</t>
+          <t>40,24; 73,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,98; 69,43</t>
+          <t>25,72; 71,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,27; 88,17</t>
+          <t>52,33; 87,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,71; 100,0</t>
+          <t>29,81; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,67; 85,54</t>
+          <t>50,91; 85,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,83; 79,86</t>
+          <t>43,78; 80,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,87; 80,11</t>
+          <t>54,65; 79,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,13; 72,84</t>
+          <t>23,63; 72,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,1; 75,33</t>
+          <t>50,4; 75,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41,29; 70,56</t>
+          <t>43,71; 71,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,48; 80,95</t>
+          <t>58,39; 80,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,09; 76,71</t>
+          <t>10,26; 84,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,34; 81,7</t>
+          <t>46,56; 81,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,56; 94,67</t>
+          <t>55,58; 94,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,71; 63,15</t>
+          <t>16,51; 61,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,14; 100,0</t>
+          <t>43,86; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,8; 82,09</t>
+          <t>45,84; 83,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,34; 85,81</t>
+          <t>29,61; 80,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,14; 52,01</t>
+          <t>23,92; 52,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,93; 81,49</t>
+          <t>33,49; 81,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,07; 76,76</t>
+          <t>53,24; 78,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,95; 82,56</t>
+          <t>50,14; 82,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,79; 51,1</t>
+          <t>25,59; 50,4</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,27; 85,18</t>
+          <t>38,49; 86,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,35; 60,01</t>
+          <t>32,28; 57,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46,76; 84,04</t>
+          <t>45,74; 83,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,49; 76,95</t>
+          <t>37,96; 76,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,93; 40,16</t>
+          <t>12,26; 38,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,33; 87,8</t>
+          <t>37,1; 86,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,33; 61,61</t>
+          <t>28,2; 60,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,58; 80,48</t>
+          <t>36,41; 78,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,57; 46,33</t>
+          <t>27,0; 46,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48,47; 79,15</t>
+          <t>49,48; 79,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,04; 63,45</t>
+          <t>37,54; 62,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,04; 84,26</t>
+          <t>37,16; 83,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,58; 93,63</t>
+          <t>63,52; 92,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,34; 74,92</t>
+          <t>43,01; 76,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,85; 83,37</t>
+          <t>31,14; 85,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 72,46</t>
+          <t>9,42; 72,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,33; 81,67</t>
+          <t>35,75; 82,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,26; 85,64</t>
+          <t>51,01; 85,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 71,4</t>
+          <t>20,07; 68,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 72,55</t>
+          <t>35,44; 72,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60,24; 85,34</t>
+          <t>59,89; 86,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53,34; 76,24</t>
+          <t>52,63; 76,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,76; 71,4</t>
+          <t>31,87; 70,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 78,87</t>
+          <t>11,02; 81,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,75; 100,0</t>
+          <t>56,52; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,77; 90,86</t>
+          <t>29,27; 91,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,57; 100,0</t>
+          <t>44,32; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,14; 100,0</t>
+          <t>31,11; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,24; 85,94</t>
+          <t>42,64; 84,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,29; 83,02</t>
+          <t>29,58; 82,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56,04; 87,38</t>
+          <t>55,94; 88,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,97; 93,78</t>
+          <t>45,54; 93,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,25; 94,27</t>
+          <t>40,6; 100,0</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,46; 73,5</t>
+          <t>8,99; 73,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,29; 69,14</t>
+          <t>33,46; 70,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,72; 64,03</t>
+          <t>27,79; 63,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,54; 47,95</t>
+          <t>12,55; 47,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,81; 90,74</t>
+          <t>32,42; 90,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,23; 71,57</t>
+          <t>37,14; 71,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,79; 82,35</t>
+          <t>47,12; 81,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,66; 48,22</t>
+          <t>23,2; 49,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,37; 73,81</t>
+          <t>26,12; 74,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39,91; 64,86</t>
+          <t>40,87; 64,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43,55; 69,0</t>
+          <t>43,88; 68,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,07; 43,07</t>
+          <t>21,74; 42,94</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,5; 48,27</t>
+          <t>12,71; 48,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,13; 64,14</t>
+          <t>38,16; 63,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50,18; 87,52</t>
+          <t>46,2; 84,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50,71; 83,25</t>
+          <t>51,29; 82,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,85; 84,93</t>
+          <t>44,87; 88,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,96; 69,78</t>
+          <t>44,3; 70,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,11; 73,23</t>
+          <t>35,45; 74,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,5; 68,95</t>
+          <t>43,08; 68,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,2; 58,0</t>
+          <t>28,07; 58,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,39; 63,08</t>
+          <t>44,72; 62,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,72; 75,29</t>
+          <t>47,45; 73,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,18; 71,34</t>
+          <t>51,79; 71,51</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37,32; 76,14</t>
+          <t>36,5; 75,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,02; 82,11</t>
+          <t>35,94; 81,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40,34; 75,5</t>
+          <t>42,52; 75,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49,86; 84,13</t>
+          <t>50,97; 86,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,02; 85,07</t>
+          <t>49,94; 85,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,09; 78,66</t>
+          <t>39,4; 78,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,94; 85,21</t>
+          <t>44,84; 84,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,51; 77,65</t>
+          <t>49,26; 78,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49,22; 76,41</t>
+          <t>50,97; 76,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,11; 75,37</t>
+          <t>45,29; 74,15</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49,47; 74,26</t>
+          <t>49,28; 73,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>53,74; 77,6</t>
+          <t>54,56; 77,91</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36,34; 55,33</t>
+          <t>37,74; 55,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52,06; 64,07</t>
+          <t>52,57; 64,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53,48; 67,38</t>
+          <t>53,96; 67,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50,28; 66,3</t>
+          <t>50,95; 66,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54,64; 74,35</t>
+          <t>54,77; 75,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,01; 62,1</t>
+          <t>49,35; 62,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,09; 71,8</t>
+          <t>57,57; 71,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44,23; 56,89</t>
+          <t>44,81; 56,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,39; 60,8</t>
+          <t>46,8; 61,38</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52,43; 61,04</t>
+          <t>52,96; 61,54</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57,64; 67,45</t>
+          <t>58,11; 68,37</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>49,97; 59,18</t>
+          <t>50,05; 60,15</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>873; 6508</t>
+          <t>873; 5763</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15407; 27648</t>
+          <t>14905; 27237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4605; 13335</t>
+          <t>4939; 13660</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14964; 24769</t>
+          <t>14700; 24513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2106; 7088</t>
+          <t>2113; 7088</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12893; 23629</t>
+          <t>14063; 23639</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12930; 24107</t>
+          <t>13217; 24313</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15900; 23215</t>
+          <t>15837; 22934</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3625; 11932</t>
+          <t>3871; 11937</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33043; 48706</t>
+          <t>32589; 48548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20394; 34853</t>
+          <t>21592; 35370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33947; 46197</t>
+          <t>33323; 45973</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>792; 6023</t>
+          <t>806; 6661</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15024; 25393</t>
+          <t>14470; 25411</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10788; 18381</t>
+          <t>10791; 18311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3823; 15373</t>
+          <t>4019; 15027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3957; 8964</t>
+          <t>3932; 8964</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13858; 24836</t>
+          <t>13870; 25280</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4817; 13625</t>
+          <t>4702; 12854</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7719; 17352</t>
+          <t>7980; 17513</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5537; 13702</t>
+          <t>5631; 13692</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31936; 47083</t>
+          <t>32656; 48016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18687; 29139</t>
+          <t>17696; 29089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14881; 29489</t>
+          <t>14769; 29082</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6613; 15527</t>
+          <t>7016; 15756</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17099; 31716</t>
+          <t>17060; 30585</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10862; 19524</t>
+          <t>10626; 19494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8424; 16416</t>
+          <t>8098; 16406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4753; 16000</t>
+          <t>4885; 15278</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5321; 12187</t>
+          <t>5150; 12024</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8126; 16508</t>
+          <t>7558; 16182</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7533; 18055</t>
+          <t>8168; 17720</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24625; 42943</t>
+          <t>25027; 43151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17987; 29374</t>
+          <t>18365; 29644</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18789; 30536</t>
+          <t>18067; 30276</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6779; 15013</t>
+          <t>6621; 14936</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19695; 28554</t>
+          <t>19373; 28091</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16641; 28763</t>
+          <t>16513; 29387</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7089; 19801</t>
+          <t>7397; 20401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1024; 7096</t>
+          <t>922; 7081</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5802; 13412</t>
+          <t>5871; 13517</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19371; 31150</t>
+          <t>18554; 30915</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3642; 13003</t>
+          <t>3656; 12532</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9888; 20031</t>
+          <t>9784; 20011</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28263; 40043</t>
+          <t>28103; 40394</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39876; 57000</t>
+          <t>39346; 56985</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13748; 29964</t>
+          <t>13372; 29485</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>809; 5772</t>
+          <t>807; 5976</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7607; 13172</t>
+          <t>7444; 13172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3722; 9198</t>
+          <t>2963; 9240</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3242; 7113</t>
+          <t>3153; 7113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2431; 7806</t>
+          <t>2428; 7806</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8758; 17015</t>
+          <t>8443; 16814</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1860; 3346</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 417</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4582; 12557</t>
+          <t>4474; 12531</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18478; 28811</t>
+          <t>18443; 29079</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6191; 12632</t>
+          <t>6134; 12583</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3080; 7214</t>
+          <t>3107; 7653</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>753; 6537</t>
+          <t>800; 6527</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9495; 20984</t>
+          <t>10155; 21387</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7543; 18072</t>
+          <t>7843; 17874</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3785; 12483</t>
+          <t>3267; 12494</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2418; 9620</t>
+          <t>3437; 9628</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13185; 25347</t>
+          <t>13155; 25354</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18154; 30023</t>
+          <t>17178; 29634</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6118; 13017</t>
+          <t>6263; 13441</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5336; 14389</t>
+          <t>5093; 14439</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26248; 42654</t>
+          <t>26879; 42632</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28170; 44631</t>
+          <t>28383; 44560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11703; 22842</t>
+          <t>11530; 22770</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3410; 13170</t>
+          <t>3469; 13253</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25990; 41538</t>
+          <t>24717; 41206</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13266; 23138</t>
+          <t>12214; 22418</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22028; 36162</t>
+          <t>22280; 35851</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7523; 15640</t>
+          <t>8263; 16335</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26235; 41641</t>
+          <t>26436; 42253</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9622; 20069</t>
+          <t>9717; 20536</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>22297; 34548</t>
+          <t>21586; 34359</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13346; 26506</t>
+          <t>12828; 26517</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56488; 78492</t>
+          <t>55648; 77913</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25696; 40536</t>
+          <t>25549; 39615</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>47880; 66734</t>
+          <t>48451; 66899</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9849; 20093</t>
+          <t>9633; 20016</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10090; 19716</t>
+          <t>8629; 19667</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13961; 26129</t>
+          <t>14714; 26003</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12942; 21835</t>
+          <t>13229; 22448</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13473; 22911</t>
+          <t>13451; 22901</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9895; 19910</t>
+          <t>9974; 19983</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12817; 22783</t>
+          <t>11988; 22558</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14166; 22217</t>
+          <t>14095; 22349</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>26246; 40745</t>
+          <t>27179; 40696</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>23238; 37178</t>
+          <t>22339; 36578</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30344; 45551</t>
+          <t>30231; 45119</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29326; 42344</t>
+          <t>29771; 42515</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>44731; 68097</t>
+          <t>46445; 68865</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>147737; 181822</t>
+          <t>149176; 181649</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106766; 134514</t>
+          <t>107727; 135418</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100593; 132643</t>
+          <t>101920; 132688</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>51253; 69745</t>
+          <t>51379; 70627</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>124644; 157938</t>
+          <t>125526; 158211</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>108617; 136617</t>
+          <t>109543; 136873</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>94485; 121523</t>
+          <t>95708; 120943</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>102779; 131867</t>
+          <t>101500; 133121</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>282136; 328442</t>
+          <t>284961; 331171</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>224745; 262987</t>
+          <t>226554; 266569</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>206704; 244820</t>
+          <t>207018; 248835</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$urgencias-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 62,01</t>
+          <t>9,39; 60,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,24; 73,54</t>
+          <t>42,63; 73,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,72; 71,12</t>
+          <t>26,42; 73,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,33; 87,26</t>
+          <t>50,48; 83,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,81; 100,0</t>
+          <t>21,63; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,91; 85,58</t>
+          <t>49,17; 85,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,78; 80,54</t>
+          <t>42,15; 79,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,65; 79,15</t>
+          <t>54,58; 78,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,63; 72,87</t>
+          <t>25,12; 74,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,4; 75,08</t>
+          <t>49,79; 75,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,71; 71,61</t>
+          <t>42,45; 71,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,39; 80,56</t>
+          <t>57,28; 78,38</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 84,83</t>
+          <t>10,26; 84,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,56; 81,76</t>
+          <t>47,35; 81,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,58; 94,31</t>
+          <t>55,79; 94,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,51; 61,73</t>
+          <t>16,17; 60,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,86; 100,0</t>
+          <t>36,38; 100,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,84; 83,56</t>
+          <t>46,36; 82,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,61; 80,95</t>
+          <t>34,49; 80,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,92; 52,49</t>
+          <t>23,85; 51,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,49; 81,43</t>
+          <t>32,55; 81,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53,24; 78,28</t>
+          <t>54,19; 78,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50,14; 82,42</t>
+          <t>51,12; 84,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,59; 50,4</t>
+          <t>25,11; 50,27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,49; 86,44</t>
+          <t>38,96; 85,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,28; 57,87</t>
+          <t>32,04; 57,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,74; 83,91</t>
+          <t>43,02; 82,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37,96; 76,91</t>
+          <t>41,76; 78,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,26; 38,35</t>
+          <t>11,91; 40,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,1; 86,62</t>
+          <t>36,7; 86,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,2; 60,39</t>
+          <t>30,6; 62,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,41; 78,99</t>
+          <t>34,46; 77,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,0; 46,55</t>
+          <t>27,0; 46,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49,48; 79,88</t>
+          <t>49,82; 78,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,54; 62,91</t>
+          <t>39,27; 63,98</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,16; 83,83</t>
+          <t>39,29; 83,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,52; 92,11</t>
+          <t>63,62; 93,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,01; 76,54</t>
+          <t>43,36; 75,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,14; 85,9</t>
+          <t>35,14; 87,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 72,3</t>
+          <t>9,84; 71,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,75; 82,3</t>
+          <t>35,75; 86,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,01; 85,0</t>
+          <t>51,0; 84,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,07; 68,81</t>
+          <t>19,85; 72,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,44; 72,48</t>
+          <t>36,26; 71,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59,89; 86,09</t>
+          <t>59,27; 85,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52,63; 76,22</t>
+          <t>53,87; 77,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,87; 70,26</t>
+          <t>34,04; 70,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,02; 81,65</t>
+          <t>10,59; 79,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,52; 100,0</t>
+          <t>58,17; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,27; 91,26</t>
+          <t>37,17; 91,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,32; 100,0</t>
+          <t>43,06; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,11; 100,0</t>
+          <t>31,27; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,64; 84,93</t>
+          <t>40,57; 84,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,58; 82,85</t>
+          <t>28,96; 85,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55,94; 88,19</t>
+          <t>54,27; 86,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,54; 93,42</t>
+          <t>46,5; 93,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,6; 100,0</t>
+          <t>38,57; 100,0</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,99; 73,4</t>
+          <t>8,39; 67,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,46; 70,47</t>
+          <t>32,03; 68,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,79; 63,33</t>
+          <t>28,15; 64,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,55; 47,99</t>
+          <t>14,55; 46,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,42; 90,81</t>
+          <t>31,56; 90,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,14; 71,59</t>
+          <t>36,74; 71,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,12; 81,28</t>
+          <t>47,98; 81,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,2; 49,79</t>
+          <t>23,12; 48,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,12; 74,07</t>
+          <t>27,83; 72,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40,87; 64,82</t>
+          <t>40,56; 65,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43,88; 68,89</t>
+          <t>44,39; 69,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,74; 42,94</t>
+          <t>22,75; 43,11</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,71; 48,57</t>
+          <t>13,04; 47,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,16; 63,62</t>
+          <t>38,24; 64,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,2; 84,8</t>
+          <t>48,85; 84,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51,29; 82,53</t>
+          <t>53,67; 83,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,87; 88,7</t>
+          <t>41,57; 88,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,3; 70,81</t>
+          <t>44,25; 69,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,45; 74,93</t>
+          <t>34,31; 72,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,08; 68,57</t>
+          <t>46,26; 69,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,07; 58,02</t>
+          <t>29,06; 58,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,72; 62,61</t>
+          <t>45,66; 63,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47,45; 73,57</t>
+          <t>48,01; 75,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,79; 71,51</t>
+          <t>55,44; 73,04</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,55%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>36,5; 75,85</t>
+          <t>38,55; 75,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,94; 81,9</t>
+          <t>39,23; 80,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42,52; 75,14</t>
+          <t>41,64; 74,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,97; 86,49</t>
+          <t>46,26; 84,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,94; 85,03</t>
+          <t>49,81; 84,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,4; 78,94</t>
+          <t>38,7; 78,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,84; 84,37</t>
+          <t>45,58; 83,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,26; 78,11</t>
+          <t>49,85; 77,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50,97; 76,32</t>
+          <t>48,79; 76,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45,29; 74,15</t>
+          <t>46,21; 74,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49,28; 73,55</t>
+          <t>49,87; 74,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>54,56; 77,91</t>
+          <t>53,79; 77,63</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37,74; 55,95</t>
+          <t>37,08; 55,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52,57; 64,01</t>
+          <t>51,59; 64,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53,96; 67,83</t>
+          <t>53,55; 67,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50,95; 66,32</t>
+          <t>52,38; 66,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54,77; 75,29</t>
+          <t>54,18; 73,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,35; 62,2</t>
+          <t>48,52; 60,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>57,57; 71,94</t>
+          <t>57,41; 71,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44,81; 56,62</t>
+          <t>45,89; 57,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46,8; 61,38</t>
+          <t>47,78; 61,13</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52,96; 61,54</t>
+          <t>52,23; 61,31</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58,11; 68,37</t>
+          <t>57,67; 67,53</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>50,05; 60,15</t>
+          <t>50,82; 60,1</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40082</t>
+          <t>39623</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>873; 5763</t>
+          <t>872; 5660</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14905; 27237</t>
+          <t>15790; 27204</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4939; 13660</t>
+          <t>5074; 14190</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14700; 24513</t>
+          <t>13649; 22590</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2113; 7088</t>
+          <t>1533; 7088</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14063; 23639</t>
+          <t>13581; 23744</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13217; 24313</t>
+          <t>12725; 24048</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15837; 22934</t>
+          <t>16611; 23932</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3871; 11937</t>
+          <t>4115; 12188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32589; 48548</t>
+          <t>32196; 48647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21592; 35370</t>
+          <t>20968; 35365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33323; 45973</t>
+          <t>32921; 45050</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21640</t>
+          <t>22414</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>806; 6661</t>
+          <t>806; 6663</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14470; 25411</t>
+          <t>14716; 25411</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10791; 18311</t>
+          <t>10832; 18349</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4019; 15027</t>
+          <t>3995; 14973</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3932; 8964</t>
+          <t>3261; 8964</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13870; 25280</t>
+          <t>14027; 24914</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4702; 12854</t>
+          <t>5477; 12716</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7980; 17513</t>
+          <t>8282; 17962</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5631; 13692</t>
+          <t>5473; 13657</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32656; 48016</t>
+          <t>33242; 48147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17696; 29089</t>
+          <t>18042; 29670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14769; 29082</t>
+          <t>14925; 29874</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>25494</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7016; 15756</t>
+          <t>7103; 15674</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17060; 30585</t>
+          <t>16937; 30577</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10626; 19494</t>
+          <t>9994; 19269</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8098; 16406</t>
+          <t>9318; 17436</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4885; 15278</t>
+          <t>4747; 16011</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5150; 12024</t>
+          <t>5094; 12072</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7558; 16182</t>
+          <t>8172; 16694</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8168; 17720</t>
+          <t>7731; 17375</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25027; 43151</t>
+          <t>25029; 43262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18365; 29644</t>
+          <t>18490; 29179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18067; 30276</t>
+          <t>19249; 31361</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22160</t>
+          <t>25824</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6621; 14936</t>
+          <t>7001; 14801</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19373; 28091</t>
+          <t>19402; 28458</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16513; 29387</t>
+          <t>16649; 28971</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7397; 20401</t>
+          <t>9874; 24500</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>922; 7081</t>
+          <t>964; 7021</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5871; 13517</t>
+          <t>5872; 14134</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18554; 30915</t>
+          <t>18549; 30676</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3656; 12532</t>
+          <t>3852; 13992</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9784; 20011</t>
+          <t>10013; 19756</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28103; 40394</t>
+          <t>27809; 40180</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39346; 56985</t>
+          <t>40274; 57639</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13372; 29485</t>
+          <t>16167; 33475</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>6007</t>
         </is>
       </c>
     </row>
@@ -3041,32 +3041,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>807; 5976</t>
+          <t>775; 5793</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7444; 13172</t>
+          <t>7663; 13172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2963; 9240</t>
+          <t>3763; 9254</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3153; 7113</t>
+          <t>3226; 7491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2428; 7806</t>
+          <t>2441; 7806</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8443; 16814</t>
+          <t>8032; 16787</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4474; 12531</t>
+          <t>4381; 12899</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18443; 29079</t>
+          <t>17894; 28679</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6134; 12583</t>
+          <t>6263; 12539</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3107; 7653</t>
+          <t>3092; 8016</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>17469</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>800; 6527</t>
+          <t>746; 6008</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10155; 21387</t>
+          <t>9720; 20801</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7843; 17874</t>
+          <t>7946; 18247</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3267; 12494</t>
+          <t>3786; 12226</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3437; 9628</t>
+          <t>3346; 9607</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13155; 25354</t>
+          <t>13011; 25184</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17178; 29634</t>
+          <t>17491; 29552</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6263; 13441</t>
+          <t>6503; 13579</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5093; 14439</t>
+          <t>5426; 14221</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26879; 42632</t>
+          <t>26673; 42943</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28383; 44560</t>
+          <t>28713; 45056</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11530; 22770</t>
+          <t>12317; 23343</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>39224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28540</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>58500</t>
+          <t>73408</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3469; 13253</t>
+          <t>3557; 13094</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24717; 41206</t>
+          <t>24769; 41460</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12214; 22418</t>
+          <t>12913; 22379</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22280; 35851</t>
+          <t>29947; 46841</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8263; 16335</t>
+          <t>7654; 16353</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26436; 42253</t>
+          <t>26407; 41523</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9717; 20536</t>
+          <t>9404; 19849</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>21586; 34359</t>
+          <t>27032; 40820</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12828; 26517</t>
+          <t>13281; 26934</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55648; 77913</t>
+          <t>56823; 79138</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25549; 39615</t>
+          <t>25848; 40787</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48451; 66899</t>
+          <t>63336; 83432</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>20071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>36502</t>
+          <t>42187</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9633; 20016</t>
+          <t>10172; 19896</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8629; 19667</t>
+          <t>9420; 19236</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14714; 26003</t>
+          <t>14409; 25831</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13229; 22448</t>
+          <t>13676; 24999</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>13451; 22901</t>
+          <t>13415; 22883</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9974; 19983</t>
+          <t>9795; 19920</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11988; 22558</t>
+          <t>12185; 22220</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14095; 22349</t>
+          <t>16859; 26280</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27179; 40696</t>
+          <t>26015; 40671</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>22339; 36578</t>
+          <t>22794; 36929</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30231; 45119</t>
+          <t>30590; 45463</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29771; 42515</t>
+          <t>34095; 49209</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>132316</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>108262</t>
+          <t>120111</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>226020</t>
+          <t>252427</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>46445; 68865</t>
+          <t>45632; 68392</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>149176; 181649</t>
+          <t>146400; 181897</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>107727; 135418</t>
+          <t>106898; 135360</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>101920; 132688</t>
+          <t>115781; 146970</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>51379; 70627</t>
+          <t>50824; 69211</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>125526; 158211</t>
+          <t>123411; 153519</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>109543; 136873</t>
+          <t>109229; 136949</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>95708; 120943</t>
+          <t>106555; 133540</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>101500; 133121</t>
+          <t>103625; 132591</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>284961; 331171</t>
+          <t>281031; 329930</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>226554; 266569</t>
+          <t>224871; 263315</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>207018; 248835</t>
+          <t>230300; 272390</t>
         </is>
       </c>
     </row>
